--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2409,7 +2409,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4036-166-CM26</t>
+          <t>4036-165-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1332.45</v>
+        <v>185.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4036-165-CM26</t>
+          <t>4036-166-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>185.64</v>
+        <v>1332.45</v>
       </c>
     </row>
     <row r="35">
@@ -3812,7 +3812,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057439-2851-CM26</t>
+          <t>1057439-2519-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>73720.5</v>
+        <v>6771.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>527481-44-CM26</t>
+          <t>1057439-2851-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>18713.05</v>
+        <v>73720.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057439-2519-CM26</t>
+          <t>527481-44-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3954,17 +3954,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6771.1</v>
+        <v>18713.05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5416-360-CM26</t>
+          <t>2708-253-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2308.59</v>
+        <v>916.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2708-253-CM26</t>
+          <t>5416-360-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4076,17 +4076,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>916.3</v>
+        <v>2308.59</v>
       </c>
     </row>
     <row r="61">
@@ -5520,7 +5520,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1232565-170-CM26</t>
+          <t>1232565-172-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3826.47</v>
+        <v>168.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1232565-172-CM26</t>
+          <t>1232565-170-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>168.98</v>
+        <v>3826.47</v>
       </c>
     </row>
     <row r="86">
@@ -6125,6 +6125,128 @@
       </c>
       <c r="M93" s="2" t="n">
         <v>15946</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>5416-795-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>3394.36</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3509-346-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>570.01</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2711-513-CM25</t>
+          <t>3597-93-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>33019.61</v>
+        <v>23633.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2711-515-CM25</t>
+          <t>1232565-118-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>22084.5</v>
+        <v>5947.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5416-1342-CM25</t>
+          <t>2710-666-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2781.03</v>
+        <v>3212.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1461054-456-CM25</t>
+          <t>527481-94-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>68864.67999999999</v>
+        <v>7382.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1461054-457-CM25</t>
+          <t>646-129-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12307.81</v>
+        <v>8037.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2711-538-CM25</t>
+          <t>2711-481-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10310.54</v>
+        <v>7943.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5416-1428-CM25</t>
+          <t>2711-513-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6007.6</v>
+        <v>33019.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2446-2136-CM25</t>
+          <t>2711-515-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,32 +981,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>128418.26</v>
+        <v>22084.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3712-1029-CM25</t>
+          <t>5416-1342-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4403</v>
+        <v>2781.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3753-283-CM25</t>
+          <t>1461054-456-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,43 +1118,43 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5700.3</v>
+        <v>68864.67999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1232565-502-CM25</t>
+          <t>2711-538-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,28 +1179,28 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>555.23</v>
+        <v>10310.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1232565-501-CM25</t>
+          <t>1461054-457-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2315.47</v>
+        <v>12307.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2450-1043-CM25</t>
+          <t>5416-1428-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,28 +1301,28 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>20539.4</v>
+        <v>6007.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1232565-499-CM25</t>
+          <t>2446-2136-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,43 +1347,47 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>9326.110000000001</v>
+        <v>128418.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1232565-500-CM25</t>
+          <t>3712-1029-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>986.15</v>
+        <v>4403</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1232565-530-CM25</t>
+          <t>3753-283-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,22 +1448,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1568.4</v>
+        <v>5700.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2288-955-CM25</t>
+          <t>2450-1043-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>9387.790000000001</v>
+        <v>20539.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057439-20521-CM25</t>
+          <t>1232565-499-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1972.28</v>
+        <v>9326.110000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057439-20524-CM25</t>
+          <t>1232565-500-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8326.68</v>
+        <v>986.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5158-205-CM25</t>
+          <t>1232565-502-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3111.23</v>
+        <v>555.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3712-12-CM26</t>
+          <t>1232565-501-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9424.66</v>
+        <v>2315.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1232565-35-CM26</t>
+          <t>1232565-530-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1239.96</v>
+        <v>1568.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3714-5-CM26</t>
+          <t>2288-955-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7771.77</v>
+        <v>9387.790000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2710-64-CM26</t>
+          <t>1057439-20521-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>39890.93</v>
+        <v>1972.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3872-39-CM26</t>
+          <t>1057439-20524-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1594.36</v>
+        <v>8326.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1395-84-CM26</t>
+          <t>5158-205-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4263.44</v>
+        <v>3111.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3688-85-CM26</t>
+          <t>3712-12-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,27 +2114,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>12215.11</v>
+        <v>9424.66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1461054-82-CM26</t>
+          <t>1232565-35-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>30716.28</v>
+        <v>1239.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1004823-19-CM26</t>
+          <t>3714-5-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,27 +2236,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.999.280-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>18724.41</v>
+        <v>7771.77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2288-277-CM26</t>
+          <t>2710-64-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>9389.1</v>
+        <v>39890.93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4036-167-CM26</t>
+          <t>3872-39-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,27 +2358,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3277.26</v>
+        <v>1594.36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4036-165-CM26</t>
+          <t>1395-84-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,27 +2419,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>185.64</v>
+        <v>4263.44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4036-166-CM26</t>
+          <t>3688-85-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1332.45</v>
+        <v>12215.11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4036-163-CM26</t>
+          <t>1461054-82-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2546,22 +2546,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>541.45</v>
+        <v>30716.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4036-162-CM26</t>
+          <t>1004823-19-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5717.21</v>
+        <v>18724.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4036-164-CM26</t>
+          <t>2288-277-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2668,22 +2668,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>946.05</v>
+        <v>9389.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4036-173-CM26</t>
+          <t>4036-167-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2554.34</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4036-178-CM26</t>
+          <t>4036-166-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>791</v>
+        <v>1332.45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3597-190-CM26</t>
+          <t>4036-165-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>16749.25</v>
+        <v>185.64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3509-108-CM26</t>
+          <t>4036-163-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2665.6</v>
+        <v>541.45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3712-214-CM26</t>
+          <t>4036-162-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3634.26</v>
+        <v>5717.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3713-39-CM26</t>
+          <t>4036-164-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11320.18</v>
+        <v>946.05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3597-233-CM26</t>
+          <t>4036-173-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3248.7</v>
+        <v>2554.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1232565-70-CM26</t>
+          <t>4036-178-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3151,27 +3151,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2442.24</v>
+        <v>791</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057439-2485-CM26</t>
+          <t>3597-190-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,27 +3212,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>14359.25</v>
+        <v>16749.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3714-81-CM26</t>
+          <t>3509-108-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,27 +3273,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>6958.05</v>
+        <v>2665.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057831-6-CM26</t>
+          <t>3712-214-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,27 +3334,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7778.55</v>
+        <v>3634.26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3509-140-CM26</t>
+          <t>3713-39-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1583.53</v>
+        <v>11320.18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3712-292-CM26</t>
+          <t>3597-233-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3461,22 +3461,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3028.55</v>
+        <v>3248.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1232565-79-CM26</t>
+          <t>1232565-70-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1846.88</v>
+        <v>2442.24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1232565-80-CM26</t>
+          <t>1057439-2485-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>585.48</v>
+        <v>14359.25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3872-126-CM26</t>
+          <t>3714-81-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3644,22 +3644,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10828.05</v>
+        <v>6958.05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1284073-9-CM26</t>
+          <t>1057831-6-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3705,22 +3705,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>48928.12</v>
+        <v>7778.55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1284073-10-CM26</t>
+          <t>3509-140-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2296.15</v>
+        <v>1583.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057439-2519-CM26</t>
+          <t>3712-292-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6771.1</v>
+        <v>3028.55</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057439-2851-CM26</t>
+          <t>1232565-79-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>73720.5</v>
+        <v>1846.88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>527481-44-CM26</t>
+          <t>1232565-80-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3949,22 +3949,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>18713.05</v>
+        <v>585.48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2708-253-CM26</t>
+          <t>3872-126-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>916.3</v>
+        <v>10828.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5416-360-CM26</t>
+          <t>1284073-9-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4071,22 +4071,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2308.59</v>
+        <v>48928.12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057439-2925-CM26</t>
+          <t>1284073-10-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4132,22 +4132,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>77178.95</v>
+        <v>2296.15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057439-2926-CM26</t>
+          <t>527481-44-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>15987.89</v>
+        <v>18713.05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5416-379-CM26</t>
+          <t>1057439-2851-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4249,27 +4249,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2770.32</v>
+        <v>73720.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5416-405-CM26</t>
+          <t>1057439-2519-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>447.43</v>
+        <v>6771.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5416-433-CM26</t>
+          <t>5416-360-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>604.51</v>
+        <v>2308.59</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1002588-131-CM26</t>
+          <t>2708-253-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4432,27 +4432,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>14535.74</v>
+        <v>916.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057631-2-CM26</t>
+          <t>1057439-2925-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4493,27 +4493,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>26398.26</v>
+        <v>77178.95</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1232565-113-CM26</t>
+          <t>1057439-2926-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>4921.71</v>
+        <v>15987.89</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5416-461-CM26</t>
+          <t>5416-379-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>272.03</v>
+        <v>2770.32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1232565-117-CM26</t>
+          <t>5416-405-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2918.4</v>
+        <v>447.43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3872-183-CM26</t>
+          <t>5416-433-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>11609.26</v>
+        <v>604.51</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3714-145-CM26</t>
+          <t>1002588-131-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>13879.09</v>
+        <v>14535.74</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1057439-3785-CM26</t>
+          <t>1057631-2-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4859,27 +4859,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>49385.07</v>
+        <v>26398.26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2555-85-CM26</t>
+          <t>1232565-113-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3105.86</v>
+        <v>4921.71</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>624-95-CM26</t>
+          <t>5416-461-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5026,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1817.84</v>
+        <v>272.03</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4036-272-CM26</t>
+          <t>1232565-117-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5042,27 +5042,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1005.57</v>
+        <v>2918.4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>624-96-CM26</t>
+          <t>3872-183-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4571.93</v>
+        <v>11609.26</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>624-97-CM26</t>
+          <t>3714-145-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>9575.57</v>
+        <v>13879.09</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>624-98-CM26</t>
+          <t>1057439-3785-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>9718.49</v>
+        <v>49385.07</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3712-390-CM26</t>
+          <t>2555-85-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>604.47</v>
+        <v>3105.86</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5416-547-CM26</t>
+          <t>624-95-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>814.8200000000001</v>
+        <v>1817.84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1057439-4120-CM26</t>
+          <t>4036-272-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5413,22 +5413,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2980.71</v>
+        <v>1005.57</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5416-585-CM26</t>
+          <t>624-96-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>434.25</v>
+        <v>4571.93</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1232565-172-CM26</t>
+          <t>624-97-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>168.98</v>
+        <v>9575.57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1232565-170-CM26</t>
+          <t>624-98-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5606,12 +5606,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3826.47</v>
+        <v>9718.49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1461054-237-CM26</t>
+          <t>3712-390-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2824.44</v>
+        <v>604.47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1232565-180-CM26</t>
+          <t>5416-547-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2121.18</v>
+        <v>814.8200000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3707-302-CM26</t>
+          <t>1057439-4120-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>656.88</v>
+        <v>2980.71</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3714-151-CM26</t>
+          <t>5416-585-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2733.37</v>
+        <v>434.25</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3714-183-CM26</t>
+          <t>1232565-170-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>19278</v>
+        <v>3826.47</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3712-472-CM26</t>
+          <t>1232565-172-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1412.22</v>
+        <v>168.98</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3712-473-CM26</t>
+          <t>1461054-237-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6018,27 +6018,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>7061.1</v>
+        <v>2824.44</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3714-200-CM26</t>
+          <t>1232565-180-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6079,27 +6079,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>15946</v>
+        <v>2121.18</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5416-795-CM26</t>
+          <t>3707-302-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3394.36</v>
+        <v>656.88</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3509-346-CM26</t>
+          <t>3714-151-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6201,27 +6201,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6246,6 +6246,372 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
+        <v>2733.37</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3714-183-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>19278</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3712-472-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>1412.22</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3712-473-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>7061.1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3714-200-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>15946</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5416-795-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>3394.36</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3509-346-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
         <v>570.01</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2711-25-CM25</t>
+          <t>2711-26-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17393.9</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2711-26-CM25</t>
+          <t>2711-25-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2142</v>
+        <v>17393.9</v>
       </c>
     </row>
     <row r="7">
@@ -1917,7 +1917,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4247-229-CM25</t>
+          <t>4247-230-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>15788.67</v>
+        <v>3177.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4247-230-CM25</t>
+          <t>4247-229-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3177.3</v>
+        <v>15788.67</v>
       </c>
     </row>
     <row r="27">
@@ -2100,7 +2100,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1232565-75-CM25</t>
+          <t>1232565-77-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.427.199-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2531.13</v>
+        <v>15320.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1232565-77-CM25</t>
+          <t>1232565-75-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL FELP SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.427.199-8</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>15320.06</v>
+        <v>2531.13</v>
       </c>
     </row>
     <row r="30">
@@ -3015,7 +3015,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1232565-143-CM25</t>
+          <t>1232565-144-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2375.24</v>
+        <v>2456.33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1232565-144-CM25</t>
+          <t>1232565-143-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2456.33</v>
+        <v>2375.24</v>
       </c>
     </row>
     <row r="45">
@@ -4052,7 +4052,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1232565-241-CM25</t>
+          <t>1232565-242-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4095.12</v>
+        <v>3641.33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1232565-242-CM25</t>
+          <t>1232565-241-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3641.33</v>
+        <v>4095.12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>527481-94-CM25</t>
+          <t>5416-953-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7382.97</v>
+        <v>6789.66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5416-953-CM25</t>
+          <t>527481-94-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6789.66</v>
+        <v>7382.97</v>
       </c>
     </row>
     <row r="64">
@@ -4967,7 +4967,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2997-209-CM25</t>
+          <t>2711-482-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5726.21</v>
+        <v>15805.28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2711-481-CM25</t>
+          <t>2997-209-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7943.25</v>
+        <v>5726.21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2711-482-CM25</t>
+          <t>2711-481-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>15805.28</v>
+        <v>7943.25</v>
       </c>
     </row>
     <row r="78">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5886,7 +5886,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1232565-499-CM25</t>
+          <t>1232565-502-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>9326.110000000001</v>
+        <v>555.23</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1232565-500-CM25</t>
+          <t>1232565-501-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>986.15</v>
+        <v>2315.47</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1232565-501-CM25</t>
+          <t>1232565-500-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2315.47</v>
+        <v>986.15</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1232565-502-CM25</t>
+          <t>1232565-499-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>555.23</v>
+        <v>9326.110000000001</v>
       </c>
     </row>
     <row r="94">
@@ -6374,7 +6374,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5158-205-CM25</t>
+          <t>3712-12-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3111.23</v>
+        <v>9424.66</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3712-12-CM26</t>
+          <t>1232565-35-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9424.66</v>
+        <v>1239.96</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1232565-35-CM26</t>
+          <t>3714-5-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1239.96</v>
+        <v>7771.77</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3714-5-CM26</t>
+          <t>1305532-6-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>7771.77</v>
+        <v>7255.43</v>
       </c>
     </row>
     <row r="102">
@@ -6801,7 +6801,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3688-85-CM26</t>
+          <t>1107276-42-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6811,27 +6811,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>12215.11</v>
+        <v>1461.46</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1461054-82-CM26</t>
+          <t>3688-85-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6877,22 +6877,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>30716.28</v>
+        <v>12215.11</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1004823-19-CM26</t>
+          <t>1461054-82-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6943,17 +6943,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.999.280-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>18724.41</v>
+        <v>30716.28</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2288-277-CM26</t>
+          <t>1004823-19-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6999,22 +6999,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>9389.1</v>
+        <v>18724.41</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4036-167-CM26</t>
+          <t>2288-277-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7060,22 +7060,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3277.26</v>
+        <v>9389.1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4036-166-CM26</t>
+          <t>4036-162-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1332.45</v>
+        <v>5717.21</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4036-165-CM26</t>
+          <t>4036-163-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>185.64</v>
+        <v>541.45</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4036-163-CM26</t>
+          <t>4036-164-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>541.45</v>
+        <v>946.05</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4036-162-CM26</t>
+          <t>4036-165-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5717.21</v>
+        <v>185.64</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4036-164-CM26</t>
+          <t>4036-166-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>946.05</v>
+        <v>1332.45</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4036-173-CM26</t>
+          <t>4036-167-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2554.34</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="116">
@@ -7533,7 +7533,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3597-190-CM26</t>
+          <t>4036-173-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>16749.25</v>
+        <v>2554.34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3509-108-CM26</t>
+          <t>3597-190-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2665.6</v>
+        <v>16749.25</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3712-214-CM26</t>
+          <t>3509-108-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3634.26</v>
+        <v>2665.6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3713-39-CM26</t>
+          <t>3712-214-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>11320.18</v>
+        <v>3634.26</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3597-233-CM26</t>
+          <t>3713-39-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3248.7</v>
+        <v>11320.18</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1232565-70-CM26</t>
+          <t>1305532-21-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2442.24</v>
+        <v>663.98</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1057439-2485-CM26</t>
+          <t>3597-233-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7914,22 +7914,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>14359.25</v>
+        <v>3248.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3714-81-CM26</t>
+          <t>1232565-70-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>6958.05</v>
+        <v>2442.24</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1057831-6-CM26</t>
+          <t>1057439-2485-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>7778.55</v>
+        <v>14359.25</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3509-140-CM26</t>
+          <t>3714-81-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8097,22 +8097,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1583.53</v>
+        <v>6958.05</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1232565-80-CM26</t>
+          <t>1057831-6-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>585.48</v>
+        <v>7778.55</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3712-292-CM26</t>
+          <t>3509-140-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8219,22 +8219,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3028.55</v>
+        <v>1583.53</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1232565-79-CM26</t>
+          <t>1232565-80-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8320,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1846.88</v>
+        <v>585.48</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3872-126-CM26</t>
+          <t>1232565-79-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8341,22 +8341,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>10828.05</v>
+        <v>1846.88</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1284073-9-CM26</t>
+          <t>3712-292-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8402,22 +8402,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>48928.12</v>
+        <v>3028.55</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1284073-10-CM26</t>
+          <t>3872-126-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8463,22 +8463,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2296.15</v>
+        <v>10828.05</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1057439-2519-CM26</t>
+          <t>1284073-9-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>6771.1</v>
+        <v>48928.12</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1057439-2851-CM26</t>
+          <t>1284073-10-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8585,22 +8585,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>73720.5</v>
+        <v>2296.15</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>527481-44-CM26</t>
+          <t>1057439-2519-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8651,17 +8651,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>18713.05</v>
+        <v>6771.1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5416-360-CM26</t>
+          <t>1057439-2851-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2308.59</v>
+        <v>73720.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2708-253-CM26</t>
+          <t>527481-44-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>916.3</v>
+        <v>18713.05</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1057439-2925-CM26</t>
+          <t>5416-360-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8829,22 +8829,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>77178.95</v>
+        <v>2308.59</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1057439-2926-CM26</t>
+          <t>2708-253-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8890,22 +8890,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>15987.89</v>
+        <v>916.3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5416-379-CM26</t>
+          <t>1057439-2925-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8946,27 +8946,27 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2770.32</v>
+        <v>77178.95</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5416-405-CM26</t>
+          <t>1057439-2926-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>447.43</v>
+        <v>15987.89</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5416-433-CM26</t>
+          <t>5416-379-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>604.51</v>
+        <v>2770.32</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1002588-131-CM26</t>
+          <t>5416-405-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>14535.74</v>
+        <v>447.43</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1057631-2-CM26</t>
+          <t>1305532-31-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>26398.26</v>
+        <v>9674.700000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1232565-113-CM26</t>
+          <t>5416-433-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4921.71</v>
+        <v>604.51</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5416-461-CM26</t>
+          <t>1002588-131-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>272.03</v>
+        <v>14535.74</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1232565-117-CM26</t>
+          <t>1057631-2-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2918.4</v>
+        <v>26398.26</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3872-183-CM26</t>
+          <t>1232565-113-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>11609.26</v>
+        <v>4921.71</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3714-145-CM26</t>
+          <t>5416-461-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>13879.09</v>
+        <v>272.03</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1057439-3785-CM26</t>
+          <t>1232565-117-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9556,27 +9556,27 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>49385.07</v>
+        <v>2918.4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2555-85-CM26</t>
+          <t>3872-183-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3105.86</v>
+        <v>11609.26</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>624-95-CM26</t>
+          <t>3714-145-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1817.84</v>
+        <v>13879.09</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4036-272-CM26</t>
+          <t>1057439-3785-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1005.57</v>
+        <v>49385.07</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>624-96-CM26</t>
+          <t>2555-85-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9845,13 +9845,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4571.93</v>
+        <v>3105.86</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>624-97-CM26</t>
+          <t>624-98-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>9575.57</v>
+        <v>9718.49</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>624-98-CM26</t>
+          <t>624-97-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>9718.49</v>
+        <v>9575.57</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3712-390-CM26</t>
+          <t>624-95-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10028,13 +10028,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>604.47</v>
+        <v>1817.84</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5416-547-CM26</t>
+          <t>4036-272-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10049,22 +10049,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>814.8200000000001</v>
+        <v>1005.57</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1057439-4120-CM26</t>
+          <t>624-96-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2980.71</v>
+        <v>4571.93</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5416-585-CM26</t>
+          <t>3712-390-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>434.25</v>
+        <v>604.47</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1232565-170-CM26</t>
+          <t>5416-547-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3826.47</v>
+        <v>814.8200000000001</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1232565-172-CM26</t>
+          <t>1057439-4120-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>168.98</v>
+        <v>2980.71</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1461054-237-CM26</t>
+          <t>5416-585-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2824.44</v>
+        <v>434.25</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1232565-180-CM26</t>
+          <t>1232565-170-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10455,13 +10455,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2121.18</v>
+        <v>3826.47</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3707-302-CM26</t>
+          <t>1232565-172-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>656.88</v>
+        <v>168.98</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3714-151-CM26</t>
+          <t>1461054-237-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10532,12 +10532,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2733.37</v>
+        <v>2824.44</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3714-183-CM26</t>
+          <t>1305532-43-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10593,12 +10593,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>19278</v>
+        <v>5091.77</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3712-472-CM26</t>
+          <t>1232565-180-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10699,13 +10699,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1412.22</v>
+        <v>2121.18</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3712-473-CM26</t>
+          <t>3707-302-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10720,22 +10720,22 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10760,13 +10760,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>7061.1</v>
+        <v>656.88</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3714-200-CM26</t>
+          <t>3714-151-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10821,13 +10821,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>15946</v>
+        <v>2733.37</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1232565-212-CM26</t>
+          <t>3714-183-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10837,12 +10837,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10882,13 +10882,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3160.64</v>
+        <v>19278</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3884-393-CM26</t>
+          <t>3712-472-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10898,27 +10898,27 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10943,13 +10943,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>296.31</v>
+        <v>1412.22</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3884-392-CM26</t>
+          <t>3712-473-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10959,27 +10959,27 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11004,13 +11004,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3211.07</v>
+        <v>7061.1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2448-760-CM26</t>
+          <t>1107276-228-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11020,27 +11020,27 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11065,13 +11065,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2252.77</v>
+        <v>983.0599999999999</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2711-202-CM26</t>
+          <t>3714-200-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>42063.91</v>
+        <v>15946</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1107276-266-CM26</t>
+          <t>2448-760-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1639.34</v>
+        <v>2252.77</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5416-795-CM26</t>
+          <t>3884-392-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11208,22 +11208,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3394.36</v>
+        <v>3211.07</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3614-241-CM26</t>
+          <t>3884-393-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11269,22 +11269,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>4746.03</v>
+        <v>296.31</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5416-846-CM26</t>
+          <t>1232565-212-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3415.31</v>
+        <v>3160.64</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1523828-23-CM26</t>
+          <t>2711-202-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>65.038.802-K</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION COQUIMBO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11416,12 +11416,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2280.04</v>
+        <v>42063.91</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1523828-24-CM26</t>
+          <t>1107276-266-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11452,22 +11452,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>65.038.802-K</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION COQUIMBO</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11492,13 +11492,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>607.76</v>
+        <v>1639.34</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1523828-25-CM26</t>
+          <t>5416-795-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11513,22 +11513,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>65.038.802-K</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11553,13 +11553,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1848.71</v>
+        <v>3394.36</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1523828-26-CM26</t>
+          <t>3614-241-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11574,22 +11574,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>65.038.802-K</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11599,12 +11599,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>101.29</v>
+        <v>4746.03</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5416-894-CM26</t>
+          <t>5416-846-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2211.02</v>
+        <v>3415.31</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3509-346-CM26</t>
+          <t>1523828-23-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>65.038.802-K</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11736,13 +11736,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>570.01</v>
+        <v>2280.04</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5416-896-CM26</t>
+          <t>1523828-24-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11757,22 +11757,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>65.038.802-K</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>569.12</v>
+        <v>607.76</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1232565-255-CM26</t>
+          <t>1523828-25-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11818,22 +11818,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>65.038.802-K</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1856.39</v>
+        <v>1848.71</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3265-442-CM26</t>
+          <t>1523828-26-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>65.038.802-K</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11904,12 +11904,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11919,13 +11919,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>20893.07</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3688-422-CM26</t>
+          <t>1232565-255-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11940,22 +11940,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11980,7 +11980,1044 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
+        <v>1856.39</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>3265-442-CM26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>69.041.000-1</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>20893.07</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>3509-346-CM26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>570.01</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>5416-894-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>IMPORTADORA HEVIA SPA</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>76.872.717-1</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>2211.02</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>5416-896-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>569.12</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>3688-422-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>69.041.400-7</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
         <v>21987.2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1232565-271-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>6512.54</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1232565-272-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>2171.99</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1471-78-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>3883.95</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1232565-295-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>1454.95</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1002588-233-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.999.320-9</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>1628.68</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>953-423-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>60.511.040-1</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>3713-120-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>12211.01</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>369-300-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>60.511.043-6</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHOAPA</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>1050.77</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1343-136-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>60.511.042-8</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LIMARÍ</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>3714-278-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>76.095.533-7</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>18798.54</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1232565-309-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>6253.94</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>369-309-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>60.511.043-6</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHOAPA</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>2142</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
@@ -562,7 +562,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1793,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1858,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1923,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1988,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2053,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2118,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2183,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2309,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2374,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2439,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2504,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2569,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2634,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2699,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2825,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2951,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3016,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3081,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3207,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3333,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3398,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3463,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3589,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3654,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3719,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3784,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3910,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4036,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4101,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4166,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4231,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4357,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4422,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4487,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4613,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4739,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4804,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4869,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4934,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4999,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5064,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5129,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5194,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5259,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5324,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5511,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5698,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5763,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6015,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6080,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6145,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6271,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6336,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6401,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6466,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6531,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6596,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6661,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6787,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6852,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6917,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +6982,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7108,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7173,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7238,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7303,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7368,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7433,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7498,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7563,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7750,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7815,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7880,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7945,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8010,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8136,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8201,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8388,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8453,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8518,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8644,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8709,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8835,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9022,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9087,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9152,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9278,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9343,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9408,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9473,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9660,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9725,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9790,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9977,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10103,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10229,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10355,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10542,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10729,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10794,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10859,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10924,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +10989,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11054,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11119,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11367,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11432,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11497,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11562,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11627,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11692,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11879,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +11944,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12009,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12074,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12139,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12204,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12330,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12395,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12460,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12586,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12712,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12838,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12903,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13029,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13155,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13220,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13285,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13350,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13415,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13541,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13606,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M206"/>
+  <dimension ref="A1:M212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1095,7 +1095,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3597-93-CM25</t>
+          <t>2710-90-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23633.4</v>
+        <v>30223.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2710-89-CM25</t>
+          <t>3597-93-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5489.47</v>
+        <v>23633.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2710-90-CM25</t>
+          <t>2710-89-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>30223.51</v>
+        <v>5489.47</v>
       </c>
     </row>
     <row r="14">
@@ -2651,7 +2651,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2710-408-CM25</t>
+          <t>2710-409-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2691,32 +2691,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>28869.45</v>
+        <v>7877.68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2710-409-CM25</t>
+          <t>2710-408-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2756,22 +2752,26 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7877.68</v>
+        <v>28869.45</v>
       </c>
     </row>
     <row r="37">
@@ -3736,7 +3736,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2710-666-CM25</t>
+          <t>624-206-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3776,32 +3776,28 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.086.318-1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3212.52</v>
+        <v>7125.72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>624-206-CM25</t>
+          <t>2710-666-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3826,12 +3822,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3841,22 +3837,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.086.318-1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7125.72</v>
+        <v>3212.52</v>
       </c>
     </row>
     <row r="54">
@@ -4183,7 +4183,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3714-266-CM25</t>
+          <t>1232565-241-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8939.280000000001</v>
+        <v>4095.12</v>
       </c>
     </row>
     <row r="60">
@@ -4309,7 +4309,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1232565-241-CM25</t>
+          <t>3714-266-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4368,13 +4368,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4095.12</v>
+        <v>8939.280000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5416-953-CM25</t>
+          <t>527481-94-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>6789.66</v>
+        <v>7382.97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>527481-94-CM25</t>
+          <t>5416-953-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4459,17 +4459,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7382.97</v>
+        <v>6789.66</v>
       </c>
     </row>
     <row r="64">
@@ -5211,7 +5211,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2711-482-CM25</t>
+          <t>2997-209-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>15805.28</v>
+        <v>5726.21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2997-209-CM25</t>
+          <t>2711-481-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5316,32 +5316,28 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>5726.21</v>
+        <v>7943.25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2711-481-CM25</t>
+          <t>2711-482-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5381,22 +5377,26 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7943.25</v>
+        <v>15805.28</v>
       </c>
     </row>
     <row r="78">
@@ -6097,7 +6097,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2450-1043-CM25</t>
+          <t>1232565-502-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6137,32 +6137,28 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>20539.4</v>
+        <v>555.23</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1232565-502-CM25</t>
+          <t>1232565-501-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6202,28 +6198,32 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>77.137.827-7</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>555.23</v>
+        <v>2315.47</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1232565-501-CM25</t>
+          <t>1232565-500-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2315.47</v>
+        <v>986.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1232565-500-CM25</t>
+          <t>1232565-499-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6347,13 +6347,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>986.15</v>
+        <v>9326.110000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1232565-499-CM25</t>
+          <t>2450-1043-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>9326.110000000001</v>
+        <v>20539.4</v>
       </c>
     </row>
     <row r="94">
@@ -7255,7 +7255,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1461054-82-CM26</t>
+          <t>1004823-19-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7275,17 +7275,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7314,13 +7314,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>30716.28</v>
+        <v>18724.41</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1004823-19-CM26</t>
+          <t>1461054-82-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7340,17 +7340,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.999.280-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>18724.41</v>
+        <v>30716.28</v>
       </c>
     </row>
     <row r="109">
@@ -7450,7 +7450,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4036-162-CM26</t>
+          <t>4036-163-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7509,13 +7509,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5717.21</v>
+        <v>541.45</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4036-163-CM26</t>
+          <t>4036-162-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7574,13 +7574,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>541.45</v>
+        <v>5717.21</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4036-164-CM26</t>
+          <t>4036-165-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>946.05</v>
+        <v>185.64</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4036-165-CM26</t>
+          <t>4036-166-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7681,28 +7681,32 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>185.64</v>
+        <v>1332.45</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4036-166-CM26</t>
+          <t>4036-167-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7742,12 +7746,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7761,13 +7765,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1332.45</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4036-167-CM26</t>
+          <t>4036-164-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7807,26 +7811,22 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3277.26</v>
+        <v>946.05</v>
       </c>
     </row>
     <row r="116">
@@ -8913,7 +8913,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1284073-9-CM26</t>
+          <t>1284073-10-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8953,28 +8953,32 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>48928.12</v>
+        <v>2296.15</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1284073-10-CM26</t>
+          <t>1284073-9-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8994,7 +8998,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -9014,26 +9018,22 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2296.15</v>
+        <v>48928.12</v>
       </c>
     </row>
     <row r="135">
@@ -9104,7 +9104,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1057439-2851-CM26</t>
+          <t>527481-44-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9124,17 +9124,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9144,32 +9144,28 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>73720.5</v>
+        <v>18713.05</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>527481-44-CM26</t>
+          <t>1057439-2851-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9189,17 +9185,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9209,22 +9205,26 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+          <t>76.872.717-1</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>18713.05</v>
+        <v>73720.5</v>
       </c>
     </row>
     <row r="138">
@@ -9360,7 +9360,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1057439-2925-CM26</t>
+          <t>1057439-2926-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9419,13 +9419,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>77178.95</v>
+        <v>15987.89</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1057439-2926-CM26</t>
+          <t>1057439-2925-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>15987.89</v>
+        <v>77178.95</v>
       </c>
     </row>
     <row r="142">
@@ -10307,7 +10307,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>624-98-CM26</t>
+          <t>4036-272-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10327,17 +10327,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10347,17 +10347,17 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10366,13 +10366,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>9718.49</v>
+        <v>1005.57</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>624-97-CM26</t>
+          <t>624-95-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -10427,13 +10427,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>9575.57</v>
+        <v>1817.84</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>624-95-CM26</t>
+          <t>624-96-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10488,13 +10488,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1817.84</v>
+        <v>4571.93</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4036-272-CM26</t>
+          <t>624-97-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10514,17 +10514,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10534,32 +10534,28 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1005.57</v>
+        <v>9575.57</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>624-96-CM26</t>
+          <t>624-98-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10599,28 +10595,32 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4571.93</v>
+        <v>9718.49</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3712-390-CM26</t>
+          <t>5416-547-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10645,12 +10645,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10660,28 +10660,32 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>604.47</v>
+        <v>814.8200000000001</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5416-547-CM26</t>
+          <t>3712-390-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10706,12 +10710,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10721,26 +10725,22 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>814.8200000000001</v>
+        <v>604.47</v>
       </c>
     </row>
     <row r="162">
@@ -11006,7 +11006,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1461054-237-CM26</t>
+          <t>1232565-180-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11046,26 +11046,22 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2824.44</v>
+        <v>2121.18</v>
       </c>
     </row>
     <row r="167">
@@ -11136,7 +11132,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1232565-180-CM26</t>
+          <t>1461054-237-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11161,12 +11157,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11176,22 +11172,26 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2121.18</v>
+        <v>2824.44</v>
       </c>
     </row>
     <row r="169">
@@ -11384,7 +11384,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3712-472-CM26</t>
+          <t>3712-473-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11443,13 +11443,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1412.22</v>
+        <v>7061.1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3712-473-CM26</t>
+          <t>3712-472-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11508,7 +11508,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>7061.1</v>
+        <v>1412.22</v>
       </c>
     </row>
     <row r="174">
@@ -11644,7 +11644,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2448-760-CM26</t>
+          <t>1232565-212-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11669,12 +11669,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -11703,13 +11703,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2252.77</v>
+        <v>3160.64</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3884-392-CM26</t>
+          <t>2448-760-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11729,17 +11729,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11749,28 +11749,32 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3211.07</v>
+        <v>2252.77</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3884-393-CM26</t>
+          <t>3884-392-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11810,12 +11814,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11825,13 +11829,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>296.31</v>
+        <v>3211.07</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1232565-212-CM26</t>
+          <t>3884-393-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11851,17 +11855,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11871,26 +11875,22 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3160.64</v>
+        <v>296.31</v>
       </c>
     </row>
     <row r="180">
@@ -12091,7 +12091,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3614-241-CM26</t>
+          <t>5416-846-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12116,12 +12116,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12131,12 +12131,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>4746.03</v>
+        <v>3415.31</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5416-846-CM26</t>
+          <t>3614-241-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12215,13 +12215,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3415.31</v>
+        <v>4746.03</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1523828-23-CM26</t>
+          <t>1523828-26-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12261,28 +12261,32 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2280.04</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1523828-24-CM26</t>
+          <t>1523828-25-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12322,12 +12326,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12341,13 +12345,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>607.76</v>
+        <v>1848.71</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1523828-25-CM26</t>
+          <t>1523828-24-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12387,12 +12391,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -12406,13 +12410,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1848.71</v>
+        <v>607.76</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1523828-26-CM26</t>
+          <t>1523828-23-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12452,26 +12456,22 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>101.29</v>
+        <v>2280.04</v>
       </c>
     </row>
     <row r="189">
@@ -12603,7 +12603,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3509-346-CM26</t>
+          <t>5416-894-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12623,17 +12623,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12643,28 +12643,32 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>76.872.717-1</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>570.01</v>
+        <v>2211.02</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5416-894-CM26</t>
+          <t>5416-896-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12704,32 +12708,28 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2211.02</v>
+        <v>569.12</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5416-896-CM26</t>
+          <t>3509-346-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12749,17 +12749,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12784,7 +12784,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>569.12</v>
+        <v>570.01</v>
       </c>
     </row>
     <row r="194">
@@ -12855,7 +12855,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1232565-271-CM26</t>
+          <t>1232565-272-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12895,32 +12895,28 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>6512.54</v>
+        <v>2171.99</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1232565-272-CM26</t>
+          <t>1232565-271-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12960,22 +12956,26 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2171.99</v>
+        <v>6512.54</v>
       </c>
     </row>
     <row r="197">
@@ -13046,7 +13046,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1232565-295-CM26</t>
+          <t>1002588-233-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13086,28 +13086,32 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1454.95</v>
+        <v>1628.68</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1002588-233-CM26</t>
+          <t>1232565-295-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13127,17 +13131,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13147,26 +13151,22 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1628.68</v>
+        <v>1454.95</v>
       </c>
     </row>
     <row r="200">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -13618,6 +13618,392 @@
       </c>
       <c r="M206" s="2" t="n">
         <v>2142</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1232565-320-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>SANDOS SPA</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>876.7</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>5416-1043-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>215.27</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>5416-1066-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>COBROTECH SPA</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>76.819.088-7</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>366.52</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1002588-254-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>61.999.320-9</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>151320.4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1523828-52-CM26</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>65.038.802-K</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>102.33</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2448-1156-CM26</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>8641.110000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
@@ -8998,7 +8998,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M212"/>
+  <dimension ref="A1:M213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -705,7 +705,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2711-26-CM25</t>
+          <t>2711-25-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -764,13 +764,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2142</v>
+        <v>17393.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2711-25-CM25</t>
+          <t>2711-26-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>17393.9</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="7">
@@ -965,7 +965,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2450-123-CM25</t>
+          <t>2450-124-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6505.73</v>
+        <v>22924.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2450-124-CM25</t>
+          <t>2450-123-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>22924.16</v>
+        <v>6505.73</v>
       </c>
     </row>
     <row r="11">
@@ -1160,7 +1160,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3597-93-CM25</t>
+          <t>2710-89-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>23633.4</v>
+        <v>5489.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2710-89-CM25</t>
+          <t>3597-93-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5489.47</v>
+        <v>23633.4</v>
       </c>
     </row>
     <row r="14">
@@ -2005,7 +2005,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4247-230-CM25</t>
+          <t>4247-229-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2064,13 +2064,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3177.3</v>
+        <v>15788.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4247-229-CM25</t>
+          <t>4247-230-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>15788.67</v>
+        <v>3177.3</v>
       </c>
     </row>
     <row r="27">
@@ -2651,7 +2651,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2710-409-CM25</t>
+          <t>2710-408-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2691,28 +2691,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7877.68</v>
+        <v>28869.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2710-408-CM25</t>
+          <t>2710-409-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2752,26 +2756,22 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>28869.45</v>
+        <v>7877.68</v>
       </c>
     </row>
     <row r="37">
@@ -3736,7 +3736,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>624-206-CM25</t>
+          <t>2710-666-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3776,28 +3776,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.086.318-1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7125.72</v>
+        <v>3212.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2710-666-CM25</t>
+          <t>624-206-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3822,12 +3826,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3837,26 +3841,22 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.086.318-1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3212.52</v>
+        <v>7125.72</v>
       </c>
     </row>
     <row r="54">
@@ -4183,7 +4183,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1232565-241-CM25</t>
+          <t>3714-266-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4095.12</v>
+        <v>8939.280000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4309,7 +4309,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3714-266-CM25</t>
+          <t>1232565-241-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4368,13 +4368,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8939.280000000001</v>
+        <v>4095.12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>527481-94-CM25</t>
+          <t>5416-953-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7382.97</v>
+        <v>6789.66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5416-953-CM25</t>
+          <t>527481-94-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4459,17 +4459,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6789.66</v>
+        <v>7382.97</v>
       </c>
     </row>
     <row r="64">
@@ -5016,7 +5016,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2711-449-CM25</t>
+          <t>2711-455-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5075,13 +5075,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4538.66</v>
+        <v>35914.03</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2711-454-CM25</t>
+          <t>2711-449-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5140,13 +5140,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>9567.059999999999</v>
+        <v>4538.66</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2711-455-CM25</t>
+          <t>2711-454-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>35914.03</v>
+        <v>9567.059999999999</v>
       </c>
     </row>
     <row r="75">
@@ -7450,7 +7450,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4036-163-CM26</t>
+          <t>4036-166-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7509,13 +7509,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>541.45</v>
+        <v>1332.45</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4036-162-CM26</t>
+          <t>4036-164-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7555,26 +7555,22 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>5717.21</v>
+        <v>946.05</v>
       </c>
     </row>
     <row r="112">
@@ -7641,7 +7637,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4036-166-CM26</t>
+          <t>4036-167-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7681,12 +7677,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7700,13 +7696,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1332.45</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4036-167-CM26</t>
+          <t>4036-162-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7746,12 +7742,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7765,13 +7761,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3277.26</v>
+        <v>5717.21</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4036-164-CM26</t>
+          <t>4036-163-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7811,28 +7807,32 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>946.05</v>
+        <v>541.45</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4036-178-CM26</t>
+          <t>4036-173-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>791</v>
+        <v>2554.34</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4036-173-CM26</t>
+          <t>4036-178-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7956,13 +7956,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2554.34</v>
+        <v>791</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3597-190-CM26</t>
+          <t>3509-108-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7987,12 +7987,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8002,32 +8002,28 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>16749.25</v>
+        <v>2665.6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3509-108-CM26</t>
+          <t>3597-190-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8052,12 +8048,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8067,22 +8063,26 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2665.6</v>
+        <v>16749.25</v>
       </c>
     </row>
     <row r="120">
@@ -9039,7 +9039,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1057439-2519-CM26</t>
+          <t>527481-44-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9059,17 +9059,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9079,32 +9079,28 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>6771.1</v>
+        <v>18713.05</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>527481-44-CM26</t>
+          <t>1057439-2519-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9124,17 +9120,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9144,22 +9140,26 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
+          <t>76.872.717-1</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>18713.05</v>
+        <v>6771.1</v>
       </c>
     </row>
     <row r="137">
@@ -9230,7 +9230,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5416-360-CM26</t>
+          <t>2708-253-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9250,17 +9250,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2308.59</v>
+        <v>916.3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2708-253-CM26</t>
+          <t>5416-360-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9315,17 +9315,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9354,13 +9354,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>916.3</v>
+        <v>2308.59</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1057439-2926-CM26</t>
+          <t>1057439-2925-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9419,13 +9419,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>15987.89</v>
+        <v>77178.95</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1057439-2925-CM26</t>
+          <t>1057439-2926-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>77178.95</v>
+        <v>15987.89</v>
       </c>
     </row>
     <row r="142">
@@ -10307,7 +10307,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4036-272-CM26</t>
+          <t>624-98-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10327,17 +10327,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10347,17 +10347,17 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10366,13 +10366,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1005.57</v>
+        <v>9718.49</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>624-95-CM26</t>
+          <t>624-97-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -10427,7 +10427,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1817.84</v>
+        <v>9575.57</v>
       </c>
     </row>
     <row r="157">
@@ -10494,7 +10494,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>624-97-CM26</t>
+          <t>4036-272-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10514,17 +10514,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10534,28 +10534,32 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>9575.57</v>
+        <v>1005.57</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>624-98-CM26</t>
+          <t>624-95-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10595,26 +10599,22 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>9718.49</v>
+        <v>1817.84</v>
       </c>
     </row>
     <row r="160">
@@ -10876,7 +10876,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1232565-170-CM26</t>
+          <t>1232565-172-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10916,12 +10916,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10935,13 +10935,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3826.47</v>
+        <v>168.98</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1232565-172-CM26</t>
+          <t>1232565-170-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>168.98</v>
+        <v>3826.47</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1232565-180-CM26</t>
+          <t>1305532-43-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11046,28 +11046,32 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2121.18</v>
+        <v>5091.77</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1305532-43-CM26</t>
+          <t>1232565-180-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11092,12 +11096,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11107,26 +11111,22 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5091.77</v>
+        <v>2121.18</v>
       </c>
     </row>
     <row r="168">
@@ -11709,7 +11709,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2448-760-CM26</t>
+          <t>3884-393-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11749,32 +11749,28 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2252.77</v>
+        <v>296.31</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3884-392-CM26</t>
+          <t>2448-760-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11799,12 +11795,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11814,28 +11810,32 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3211.07</v>
+        <v>2252.77</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3884-393-CM26</t>
+          <t>3884-392-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11890,7 +11890,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>296.31</v>
+        <v>3211.07</v>
       </c>
     </row>
     <row r="180">
@@ -12221,7 +12221,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1523828-26-CM26</t>
+          <t>1523828-23-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12261,32 +12261,28 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>101.29</v>
+        <v>2280.04</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1523828-25-CM26</t>
+          <t>1523828-24-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12326,12 +12322,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12345,13 +12341,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1848.71</v>
+        <v>607.76</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1523828-24-CM26</t>
+          <t>1523828-25-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12391,12 +12387,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -12410,13 +12406,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>607.76</v>
+        <v>1848.71</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1523828-23-CM26</t>
+          <t>1523828-26-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12456,28 +12452,32 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2280.04</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1232565-255-CM26</t>
+          <t>5416-894-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12517,22 +12517,26 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+          <t>76.872.717-1</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1856.39</v>
+        <v>2211.02</v>
       </c>
     </row>
     <row r="190">
@@ -12603,7 +12607,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5416-894-CM26</t>
+          <t>5416-896-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12643,32 +12647,28 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2211.02</v>
+        <v>569.12</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5416-896-CM26</t>
+          <t>3509-346-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12688,17 +12688,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12723,13 +12723,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>569.12</v>
+        <v>570.01</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3509-346-CM26</t>
+          <t>1232565-255-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12749,17 +12749,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12784,7 +12784,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>570.01</v>
+        <v>1856.39</v>
       </c>
     </row>
     <row r="194">
@@ -12981,7 +12981,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1471-78-CM26</t>
+          <t>1232565-295-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13001,17 +13001,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13021,26 +13021,22 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>3883.95</v>
+        <v>1454.95</v>
       </c>
     </row>
     <row r="198">
@@ -13111,7 +13107,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1232565-295-CM26</t>
+          <t>1471-78-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13131,17 +13127,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13151,22 +13147,26 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1454.95</v>
+        <v>3883.95</v>
       </c>
     </row>
     <row r="200">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -14004,6 +14004,67 @@
       </c>
       <c r="M212" s="2" t="n">
         <v>8641.110000000001</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>5416-1151-CM26</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>2903.6</v>
       </c>
     </row>
   </sheetData>
